--- a/product_selector_out/STM32F2 series - diff.xlsx
+++ b/product_selector_out/STM32F2 series - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2508</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2384</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="18">
